--- a/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_9_9.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_9_9.xlsx
@@ -517,657 +517,657 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9994814992583927</v>
+        <v>0.9998145407328221</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5825344644575603</v>
+        <v>0.6618298626895199</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9999606226942371</v>
+        <v>0.9999485371095901</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9995982564497671</v>
+        <v>0.9998861415789512</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9998328543390764</v>
+        <v>0.9999087364940561</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0003078044382839106</v>
+        <v>0.0001100966324200179</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2478255754701344</v>
+        <v>0.2007524016967964</v>
       </c>
       <c r="I2" t="n">
-        <v>1.627830359628635e-05</v>
+        <v>1.368724256749439e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0001975235518467782</v>
+        <v>9.179063526686192e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0001069017538177461</v>
+        <v>5.273893891717815e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004362433896944799</v>
+        <v>0.002101715004940108</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01754435630862274</v>
+        <v>0.01049269424028061</v>
       </c>
       <c r="N2" t="n">
-        <v>1.00020400029178</v>
+        <v>1.000072967580529</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01829125587850507</v>
+        <v>0.01093938995696077</v>
       </c>
       <c r="P2" t="n">
-        <v>186.172091834575</v>
+        <v>188.2283042025219</v>
       </c>
       <c r="Q2" t="n">
-        <v>289.7765369483721</v>
+        <v>291.8327493163189</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>model_9_9_1</t>
+          <t>model_9_9_22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9995550546206275</v>
+        <v>0.9998145407328221</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5823550710798231</v>
+        <v>0.6618298626895199</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9998684137086907</v>
+        <v>0.9999485371095901</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9995702270252902</v>
+        <v>0.9998861415789512</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9997922830765306</v>
+        <v>0.9999087364940561</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0002641387978350763</v>
+        <v>0.0001100966324200179</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2479320711285497</v>
+        <v>0.2007524016967964</v>
       </c>
       <c r="I3" t="n">
-        <v>5.439685518208825e-05</v>
+        <v>1.368724256749439e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0002113046604064114</v>
+        <v>9.179063526686192e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0001328500141362866</v>
+        <v>5.273893891717815e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004315820007163973</v>
+        <v>0.002101715004940108</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01625234745613926</v>
+        <v>0.01049269424028061</v>
       </c>
       <c r="N3" t="n">
-        <v>1.00017506047713</v>
+        <v>1.000072967580529</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01694424353434434</v>
+        <v>0.01093938995696077</v>
       </c>
       <c r="P3" t="n">
-        <v>186.4780716872009</v>
+        <v>188.2283042025219</v>
       </c>
       <c r="Q3" t="n">
-        <v>290.082516800998</v>
+        <v>291.8327493163189</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>model_9_9_2</t>
+          <t>model_9_9_21</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9996061338620464</v>
+        <v>0.9998145407328221</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5821664304938607</v>
+        <v>0.6618298626895199</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9997381778401253</v>
+        <v>0.9999485371095901</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9995300172041783</v>
+        <v>0.9998861415789512</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9997347369111488</v>
+        <v>0.9999087364940561</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0002338159536204955</v>
+        <v>0.0001100966324200179</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2480440563292259</v>
+        <v>0.2007524016967964</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0001082354550192986</v>
+        <v>1.368724256749439e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0002310744530528219</v>
+        <v>9.179063526686192e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0001696549540360603</v>
+        <v>5.273893891717815e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004273633082723455</v>
+        <v>0.002101715004940108</v>
       </c>
       <c r="M4" t="n">
-        <v>0.01529104161332692</v>
+        <v>0.01049269424028061</v>
       </c>
       <c r="N4" t="n">
-        <v>1.000154963726408</v>
+        <v>1.000072967580529</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01594201291162605</v>
+        <v>0.01093938995696077</v>
       </c>
       <c r="P4" t="n">
-        <v>186.7219525501348</v>
+        <v>188.2283042025219</v>
       </c>
       <c r="Q4" t="n">
-        <v>290.3263976639319</v>
+        <v>291.8327493163189</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>model_9_9_3</t>
+          <t>model_9_9_20</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9996398375566848</v>
+        <v>0.9998145407328221</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5819748675135097</v>
+        <v>0.6618298626895199</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9995823990615461</v>
+        <v>0.9999485371095901</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9994818254093217</v>
+        <v>0.9998861415789512</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9996658699947832</v>
+        <v>0.9999087364940561</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0002138079845593442</v>
+        <v>0.0001100966324200179</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2481577763894522</v>
+        <v>0.2007524016967964</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0001726333157272451</v>
+        <v>1.368724256749439e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0002547687089641438</v>
+        <v>9.179063526686192e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>0.000213700333968845</v>
+        <v>5.273893891717815e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004235556715281574</v>
+        <v>0.002101715004940108</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01462217441283423</v>
+        <v>0.01049269424028061</v>
       </c>
       <c r="N5" t="n">
-        <v>1.000141703256386</v>
+        <v>1.000072967580529</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01524467064966241</v>
+        <v>0.01093938995696077</v>
       </c>
       <c r="P5" t="n">
-        <v>186.9008644282859</v>
+        <v>188.2283042025219</v>
       </c>
       <c r="Q5" t="n">
-        <v>290.505309542083</v>
+        <v>291.8327493163189</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>model_9_9_4</t>
+          <t>model_9_9_19</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9996602296238518</v>
+        <v>0.9998145407328221</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5817848953151852</v>
+        <v>0.6618298626895199</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9994107045704046</v>
+        <v>0.9999485371095901</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9994288894469167</v>
+        <v>0.9998861415789512</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9995900335383088</v>
+        <v>0.9999087364940561</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0002017023725975723</v>
+        <v>0.0001100966324200179</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2482705520927493</v>
+        <v>0.2007524016967964</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0002436106210168403</v>
+        <v>1.368724256749439e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0002807955096648201</v>
+        <v>9.179063526686192e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002622032394923844</v>
+        <v>5.273893891717815e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.004201236971908925</v>
+        <v>0.002101715004940108</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01420219604841351</v>
+        <v>0.01049269424028061</v>
       </c>
       <c r="N6" t="n">
-        <v>1.000133680147993</v>
+        <v>1.000072967580529</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01480681293679323</v>
+        <v>0.01093938995696077</v>
       </c>
       <c r="P6" t="n">
-        <v>187.0174347001419</v>
+        <v>188.2283042025219</v>
       </c>
       <c r="Q6" t="n">
-        <v>290.621879813939</v>
+        <v>291.8327493163189</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>model_9_9_5</t>
+          <t>model_9_9_18</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9996705207203493</v>
+        <v>0.9998145407328221</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5815999336077123</v>
+        <v>0.6618298626895199</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9992305209387714</v>
+        <v>0.9999485371095901</v>
       </c>
       <c r="E7" t="n">
-        <v>0.999373596222089</v>
+        <v>0.9998861415789512</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9995105478204865</v>
+        <v>0.9999087364940561</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001955931331644002</v>
+        <v>0.0001100966324200179</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2483803533522349</v>
+        <v>0.2007524016967964</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0003180972777848459</v>
+        <v>1.368724256749439e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0003079812956088348</v>
+        <v>9.179063526686192e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0003130401119048758</v>
+        <v>5.273893891717815e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004170245552968808</v>
+        <v>0.002101715004940108</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01398546149272165</v>
+        <v>0.01049269424028061</v>
       </c>
       <c r="N7" t="n">
-        <v>1.000129631191994</v>
+        <v>1.000072967580529</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01458085154236319</v>
+        <v>0.01093938995696077</v>
       </c>
       <c r="P7" t="n">
-        <v>187.0789478150026</v>
+        <v>188.2283042025219</v>
       </c>
       <c r="Q7" t="n">
-        <v>290.6833929287996</v>
+        <v>291.8327493163189</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>model_9_9_6</t>
+          <t>model_9_9_17</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9996732498051896</v>
+        <v>0.9998145407328221</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5814220518027955</v>
+        <v>0.6618298626895199</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9990474401065071</v>
+        <v>0.9999485371095901</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9993177065354628</v>
+        <v>0.9998861415789512</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9994299014143978</v>
+        <v>0.9999087364940561</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0001939730305129163</v>
+        <v>0.0001100966324200179</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2484859516757274</v>
+        <v>0.2007524016967964</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0003937816170895147</v>
+        <v>1.368724256749439e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0003354603414020938</v>
+        <v>9.179063526686192e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0003646193285135418</v>
+        <v>5.273893891717815e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004142263525873578</v>
+        <v>0.002101715004940108</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01392742009537001</v>
+        <v>0.01049269424028061</v>
       </c>
       <c r="N8" t="n">
-        <v>1.000128557453696</v>
+        <v>1.000072967580529</v>
       </c>
       <c r="O8" t="n">
-        <v>0.01452033920256402</v>
+        <v>0.01093938995696077</v>
       </c>
       <c r="P8" t="n">
-        <v>187.095582853079</v>
+        <v>188.2283042025219</v>
       </c>
       <c r="Q8" t="n">
-        <v>290.7000279668761</v>
+        <v>291.8327493163189</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>model_9_9_7</t>
+          <t>model_9_9_16</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9996704192638397</v>
+        <v>0.9998145407328221</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5812529379471372</v>
+        <v>0.6618298626895199</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9988656464658345</v>
+        <v>0.9999485371095901</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9992625137570774</v>
+        <v>0.9998861415789512</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9993499324207415</v>
+        <v>0.9999087364940561</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0001956533621312106</v>
+        <v>0.0001100966324200179</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2485863449657844</v>
+        <v>0.2007524016967964</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0004689338403666673</v>
+        <v>1.368724256749439e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0003625967412687805</v>
+        <v>9.179063526686192e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0004157652908177239</v>
+        <v>5.273893891717815e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>0.00411705895173921</v>
+        <v>0.002101715004940108</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01398761459760779</v>
+        <v>0.01049269424028061</v>
       </c>
       <c r="N9" t="n">
-        <v>1.000129671109309</v>
+        <v>1.000072967580529</v>
       </c>
       <c r="O9" t="n">
-        <v>0.01458309630938187</v>
+        <v>0.01093938995696077</v>
       </c>
       <c r="P9" t="n">
-        <v>187.0783320500768</v>
+        <v>188.2283042025219</v>
       </c>
       <c r="Q9" t="n">
-        <v>290.6827771638738</v>
+        <v>291.8327493163189</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>model_9_9_8</t>
+          <t>model_9_9_15</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9996635716419745</v>
+        <v>0.9998145407328221</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5810934226494087</v>
+        <v>0.6618298626895199</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9986881372099687</v>
+        <v>0.9999485371095901</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9992089129714609</v>
+        <v>0.9998861415789512</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9992719612564219</v>
+        <v>0.9999087364940561</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0001997184062722724</v>
+        <v>0.0001100966324200179</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2486810401372181</v>
+        <v>0.2007524016967964</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0005423149288427946</v>
+        <v>1.368724256749439e-05</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0003889504127854007</v>
+        <v>9.179063526686192e-05</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0004656334965905673</v>
+        <v>5.273893891717815e-05</v>
       </c>
       <c r="L10" t="n">
-        <v>0.004094436912388082</v>
+        <v>0.002101715004940108</v>
       </c>
       <c r="M10" t="n">
-        <v>0.01413217627516273</v>
+        <v>0.01049269424028061</v>
       </c>
       <c r="N10" t="n">
-        <v>1.000132365255617</v>
+        <v>1.000072967580529</v>
       </c>
       <c r="O10" t="n">
-        <v>0.01473381227683425</v>
+        <v>0.01093938995696077</v>
       </c>
       <c r="P10" t="n">
-        <v>187.0372043043482</v>
+        <v>188.2283042025219</v>
       </c>
       <c r="Q10" t="n">
-        <v>290.6416494181452</v>
+        <v>291.8327493163189</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>model_9_9_9</t>
+          <t>model_9_9_14</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9996539372038005</v>
+        <v>0.9998145407328221</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5809440014733837</v>
+        <v>0.6618298626895199</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9985171396956561</v>
+        <v>0.9999485371095901</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9991575001697971</v>
+        <v>0.9998861415789512</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9991969381308121</v>
+        <v>0.9999087364940561</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0002054378249584318</v>
+        <v>0.0001100966324200179</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2487697430019652</v>
+        <v>0.2007524016967964</v>
       </c>
       <c r="I11" t="n">
-        <v>0.000613004108771828</v>
+        <v>1.368724256749439e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0004142283274877497</v>
+        <v>9.179063526686192e-05</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0005136162181297889</v>
+        <v>5.273893891717815e-05</v>
       </c>
       <c r="L11" t="n">
-        <v>0.004073854410076024</v>
+        <v>0.002101715004940108</v>
       </c>
       <c r="M11" t="n">
-        <v>0.01433310241917052</v>
+        <v>0.01049269424028061</v>
       </c>
       <c r="N11" t="n">
-        <v>1.000136155854243</v>
+        <v>1.000072967580529</v>
       </c>
       <c r="O11" t="n">
-        <v>0.01494329226276691</v>
+        <v>0.01093938995696077</v>
       </c>
       <c r="P11" t="n">
-        <v>186.9807342495075</v>
+        <v>188.2283042025219</v>
       </c>
       <c r="Q11" t="n">
-        <v>290.5851793633046</v>
+        <v>291.8327493163189</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>model_9_9_10</t>
+          <t>model_9_9_13</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9996424513545845</v>
+        <v>0.9998145407328221</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5808047733751946</v>
+        <v>0.6618298626895199</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9983540760650865</v>
+        <v>0.9999485371095901</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9991087240163601</v>
+        <v>0.9998861415789512</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9991254899388202</v>
+        <v>0.9999087364940561</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0002122563212158644</v>
+        <v>0.0001100966324200179</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2488523948153909</v>
+        <v>0.2007524016967964</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0006804134764901656</v>
+        <v>1.368724256749439e-05</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0004382098925103434</v>
+        <v>9.179063526686192e-05</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0005593125107456823</v>
+        <v>5.273893891717815e-05</v>
       </c>
       <c r="L12" t="n">
-        <v>0.004055418432048449</v>
+        <v>0.002101715004940108</v>
       </c>
       <c r="M12" t="n">
-        <v>0.01456901922628508</v>
+        <v>0.01049269424028061</v>
       </c>
       <c r="N12" t="n">
-        <v>1.000140674876885</v>
+        <v>1.000072967580529</v>
       </c>
       <c r="O12" t="n">
-        <v>0.01518925253677545</v>
+        <v>0.01093938995696077</v>
       </c>
       <c r="P12" t="n">
-        <v>186.9154319025611</v>
+        <v>188.2283042025219</v>
       </c>
       <c r="Q12" t="n">
-        <v>290.5198770163581</v>
+        <v>291.8327493163189</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>model_9_9_11</t>
+          <t>model_9_9_23</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9996298262132531</v>
+        <v>0.9998145407328221</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5806755933547451</v>
+        <v>0.6618298626895199</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9981998465195855</v>
+        <v>0.9999485371095901</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9990627607090445</v>
+        <v>0.9998861415789512</v>
       </c>
       <c r="F13" t="n">
-        <v>0.999057983554571</v>
+        <v>0.9999087364940561</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0002197511504879184</v>
+        <v>0.0001100966324200179</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2489290816558161</v>
+        <v>0.2007524016967964</v>
       </c>
       <c r="I13" t="n">
-        <v>0.000744170895047525</v>
+        <v>1.368724256749439e-05</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0004608084773795063</v>
+        <v>9.179063526686192e-05</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0006024877318688126</v>
+        <v>5.273893891717815e-05</v>
       </c>
       <c r="L13" t="n">
-        <v>0.004038798363456948</v>
+        <v>0.002101715004940108</v>
       </c>
       <c r="M13" t="n">
-        <v>0.01482400588531718</v>
+        <v>0.01049269424028061</v>
       </c>
       <c r="N13" t="n">
-        <v>1.000145642145605</v>
+        <v>1.000072967580529</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0154550945057777</v>
+        <v>0.01093938995696077</v>
       </c>
       <c r="P13" t="n">
-        <v>186.8460295719456</v>
+        <v>188.2283042025219</v>
       </c>
       <c r="Q13" t="n">
-        <v>290.4504746857426</v>
+        <v>291.8327493163189</v>
       </c>
     </row>
     <row r="14">
@@ -1177,657 +1177,657 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9996166182501042</v>
+        <v>0.9998145407328221</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5805562971286419</v>
+        <v>0.6618298626895199</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9980549788722798</v>
+        <v>0.9999485371095901</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9990197920854185</v>
+        <v>0.9998861415789512</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9989946451139877</v>
+        <v>0.9999087364940561</v>
       </c>
       <c r="G14" t="n">
-        <v>0.00022759196796743</v>
+        <v>0.0001100966324200179</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2489999010489596</v>
+        <v>0.2007524016967964</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0008040581701781235</v>
+        <v>1.368724256749439e-05</v>
       </c>
       <c r="J14" t="n">
-        <v>0.000481934678787526</v>
+        <v>9.179063526686192e-05</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0006429972512007635</v>
+        <v>5.273893891717815e-05</v>
       </c>
       <c r="L14" t="n">
-        <v>0.004023803116513187</v>
+        <v>0.002101715004940108</v>
       </c>
       <c r="M14" t="n">
-        <v>0.01508615152938051</v>
+        <v>0.01049269424028061</v>
       </c>
       <c r="N14" t="n">
-        <v>1.000150838721271</v>
+        <v>1.000072967580529</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0157284002326251</v>
+        <v>0.01093938995696077</v>
       </c>
       <c r="P14" t="n">
-        <v>186.7759122929207</v>
+        <v>188.2283042025219</v>
       </c>
       <c r="Q14" t="n">
-        <v>290.3803574067177</v>
+        <v>291.8327493163189</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>model_9_9_13</t>
+          <t>model_9_9_10</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9996032351655383</v>
+        <v>0.9998145407328221</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5804463674592357</v>
+        <v>0.6618298626895199</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9979197197038285</v>
+        <v>0.9999485371095901</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9989798053703161</v>
+        <v>0.9998861415789512</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9989355637332341</v>
+        <v>0.9999087364940561</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0002355367450848819</v>
+        <v>0.0001100966324200179</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2490651600494335</v>
+        <v>0.2007524016967964</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0008599733671571073</v>
+        <v>1.368724256749439e-05</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0005015947778461013</v>
+        <v>9.179063526686192e-05</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0006807840725016043</v>
+        <v>5.273893891717815e-05</v>
       </c>
       <c r="L15" t="n">
-        <v>0.004010374161023548</v>
+        <v>0.002101715004940108</v>
       </c>
       <c r="M15" t="n">
-        <v>0.01534720642608556</v>
+        <v>0.01049269424028061</v>
       </c>
       <c r="N15" t="n">
-        <v>1.000156104197165</v>
+        <v>1.000072967580529</v>
       </c>
       <c r="O15" t="n">
-        <v>0.01600056877674101</v>
+        <v>0.01093938995696077</v>
       </c>
       <c r="P15" t="n">
-        <v>186.7072872531896</v>
+        <v>188.2283042025219</v>
       </c>
       <c r="Q15" t="n">
-        <v>290.3117323669867</v>
+        <v>291.8327493163189</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>model_9_9_14</t>
+          <t>model_9_9_9</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9995899663638345</v>
+        <v>0.9998145407328221</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5803454119045683</v>
+        <v>0.6618298626895199</v>
       </c>
       <c r="D16" t="n">
-        <v>0.997793927132018</v>
+        <v>0.9999485371095901</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9989427228185385</v>
+        <v>0.9998861415789512</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9988806572625216</v>
+        <v>0.9999087364940561</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0002434136789586847</v>
+        <v>0.0001100966324200179</v>
       </c>
       <c r="H16" t="n">
-        <v>0.249125091627737</v>
+        <v>0.2007524016967964</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0009119751391021447</v>
+        <v>1.368724256749439e-05</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0005198269992081961</v>
+        <v>9.179063526686192e-05</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0007159007365099535</v>
+        <v>5.273893891717815e-05</v>
       </c>
       <c r="L16" t="n">
-        <v>0.00399827495142886</v>
+        <v>0.002101715004940108</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0156017203845821</v>
+        <v>0.01049269424028061</v>
       </c>
       <c r="N16" t="n">
-        <v>1.000161324709311</v>
+        <v>1.000072967580529</v>
       </c>
       <c r="O16" t="n">
-        <v>0.01626591792136728</v>
+        <v>0.01093938995696077</v>
       </c>
       <c r="P16" t="n">
-        <v>186.6414963589768</v>
+        <v>188.2283042025219</v>
       </c>
       <c r="Q16" t="n">
-        <v>290.2459414727738</v>
+        <v>291.8327493163189</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>model_9_9_15</t>
+          <t>model_9_9_8</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9995770506911663</v>
+        <v>0.9998145407328221</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5802529343583751</v>
+        <v>0.6618298626895199</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9976775415070727</v>
+        <v>0.9999485371095901</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9989085146287022</v>
+        <v>0.9998861415789512</v>
       </c>
       <c r="F17" t="n">
-        <v>0.998829893408182</v>
+        <v>0.9999087364940561</v>
       </c>
       <c r="G17" t="n">
-        <v>0.000251080980182488</v>
+        <v>0.0001100966324200179</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2491799902939793</v>
+        <v>0.2007524016967964</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0009600881448144699</v>
+        <v>1.368724256749439e-05</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0005366459951940395</v>
+        <v>9.179063526686192e-05</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0007483678973652346</v>
+        <v>5.273893891717815e-05</v>
       </c>
       <c r="L17" t="n">
-        <v>0.003987244938487102</v>
+        <v>0.002101715004940108</v>
       </c>
       <c r="M17" t="n">
-        <v>0.01584553502354805</v>
+        <v>0.01049269424028061</v>
       </c>
       <c r="N17" t="n">
-        <v>1.000166406285443</v>
+        <v>1.000072967580529</v>
       </c>
       <c r="O17" t="n">
-        <v>0.01652011225427989</v>
+        <v>0.01093938995696077</v>
       </c>
       <c r="P17" t="n">
-        <v>186.5794700813146</v>
+        <v>188.2283042025219</v>
       </c>
       <c r="Q17" t="n">
-        <v>290.1839151951117</v>
+        <v>291.8327493163189</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>model_9_9_16</t>
+          <t>model_9_9_7</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9995646334320845</v>
+        <v>0.9998145407328221</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5801684076843703</v>
+        <v>0.6618298626895199</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9975701955157914</v>
+        <v>0.9999485371095901</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9988770417804002</v>
+        <v>0.9998861415789512</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9987831054680171</v>
+        <v>0.9999087364940561</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0002584524015711104</v>
+        <v>0.0001100966324200179</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2492301689790307</v>
+        <v>0.2007524016967964</v>
       </c>
       <c r="I18" t="n">
-        <v>0.001004464229009872</v>
+        <v>1.368724256749439e-05</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0005521201173791079</v>
+        <v>9.179063526686192e-05</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0007782921731944899</v>
+        <v>5.273893891717815e-05</v>
       </c>
       <c r="L18" t="n">
-        <v>0.003977380234865865</v>
+        <v>0.002101715004940108</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0160764548819418</v>
+        <v>0.01049269424028061</v>
       </c>
       <c r="N18" t="n">
-        <v>1.000171291764426</v>
+        <v>1.000072967580529</v>
       </c>
       <c r="O18" t="n">
-        <v>0.01676086284911547</v>
+        <v>0.01093938995696077</v>
       </c>
       <c r="P18" t="n">
-        <v>186.5215980283152</v>
+        <v>188.2283042025219</v>
       </c>
       <c r="Q18" t="n">
-        <v>290.1260431421122</v>
+        <v>291.8327493163189</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>model_9_9_17</t>
+          <t>model_9_9_6</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9995528036197543</v>
+        <v>0.9998145407328221</v>
       </c>
       <c r="C19" t="n">
-        <v>0.5800912569632304</v>
+        <v>0.6618298626895199</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9974713616031143</v>
+        <v>0.9999485371095901</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9988481742379172</v>
+        <v>0.9998861415789512</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9987400698584968</v>
+        <v>0.9999087364940561</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0002654750891915929</v>
+        <v>0.0001100966324200179</v>
       </c>
       <c r="H19" t="n">
-        <v>0.249275968979837</v>
+        <v>0.2007524016967964</v>
       </c>
       <c r="I19" t="n">
-        <v>0.001045321479271126</v>
+        <v>1.368724256749439e-05</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0005663132998733136</v>
+        <v>9.179063526686192e-05</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0008058165618559684</v>
+        <v>5.273893891717815e-05</v>
       </c>
       <c r="L19" t="n">
-        <v>0.003968519442068502</v>
+        <v>0.002101715004940108</v>
       </c>
       <c r="M19" t="n">
-        <v>0.01629340631027143</v>
+        <v>0.01049269424028061</v>
       </c>
       <c r="N19" t="n">
-        <v>1.000175946116818</v>
+        <v>1.000072967580529</v>
       </c>
       <c r="O19" t="n">
-        <v>0.01698705034890046</v>
+        <v>0.01093938995696077</v>
       </c>
       <c r="P19" t="n">
-        <v>186.4679790954092</v>
+        <v>188.2283042025219</v>
       </c>
       <c r="Q19" t="n">
-        <v>290.0724242092062</v>
+        <v>291.8327493163189</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>model_9_9_18</t>
+          <t>model_9_9_5</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9995416372735413</v>
+        <v>0.9998145407328221</v>
       </c>
       <c r="C20" t="n">
-        <v>0.580020989400341</v>
+        <v>0.6618298626895199</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9973807175365113</v>
+        <v>0.9999485371095901</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9988217340600897</v>
+        <v>0.9998861415789512</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9987006114564991</v>
+        <v>0.9999087364940561</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0002721039146647264</v>
+        <v>0.0001100966324200179</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2493176828405688</v>
+        <v>0.2007524016967964</v>
       </c>
       <c r="I20" t="n">
-        <v>0.001082793104279025</v>
+        <v>1.368724256749439e-05</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0005793130302558239</v>
+        <v>9.179063526686192e-05</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0008310530672674246</v>
+        <v>5.273893891717815e-05</v>
       </c>
       <c r="L20" t="n">
-        <v>0.003960557634965327</v>
+        <v>0.002101715004940108</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0164955725776563</v>
+        <v>0.01049269424028061</v>
       </c>
       <c r="N20" t="n">
-        <v>1.000180339433361</v>
+        <v>1.000072967580529</v>
       </c>
       <c r="O20" t="n">
-        <v>0.01719782325282977</v>
+        <v>0.01093938995696077</v>
       </c>
       <c r="P20" t="n">
-        <v>186.4186530508362</v>
+        <v>188.2283042025219</v>
       </c>
       <c r="Q20" t="n">
-        <v>290.0230981646333</v>
+        <v>291.8327493163189</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>model_9_9_19</t>
+          <t>model_9_9_4</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9995311627220825</v>
+        <v>0.9998145407328221</v>
       </c>
       <c r="C21" t="n">
-        <v>0.5799570580033513</v>
+        <v>0.6618298626895199</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9972977281236998</v>
+        <v>0.9999485371095901</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9987975756496734</v>
+        <v>0.9998861415789512</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9986645046444812</v>
+        <v>0.9999087364940561</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0002783220608876898</v>
+        <v>0.0001100966324200179</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2493556352795145</v>
+        <v>0.2007524016967964</v>
       </c>
       <c r="I21" t="n">
-        <v>0.001117100348790822</v>
+        <v>1.368724256749439e-05</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0005911908937078243</v>
+        <v>9.179063526686192e-05</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0008541459881853326</v>
+        <v>5.273893891717815e-05</v>
       </c>
       <c r="L21" t="n">
-        <v>0.003953396373287229</v>
+        <v>0.002101715004940108</v>
       </c>
       <c r="M21" t="n">
-        <v>0.01668298716919994</v>
+        <v>0.01049269424028061</v>
       </c>
       <c r="N21" t="n">
-        <v>1.000184460568361</v>
+        <v>1.000072967580529</v>
       </c>
       <c r="O21" t="n">
-        <v>0.01739321647153711</v>
+        <v>0.01093938995696077</v>
       </c>
       <c r="P21" t="n">
-        <v>186.3734632448127</v>
+        <v>188.2283042025219</v>
       </c>
       <c r="Q21" t="n">
-        <v>289.9779083586098</v>
+        <v>291.8327493163189</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>model_9_9_20</t>
+          <t>model_9_9_3</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9995213912647438</v>
+        <v>0.9998145407328221</v>
       </c>
       <c r="C22" t="n">
-        <v>0.5798989306848625</v>
+        <v>0.6618298626895199</v>
       </c>
       <c r="D22" t="n">
-        <v>0.997221901129838</v>
+        <v>0.9999485371095901</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9987755285309696</v>
+        <v>0.9998861415789512</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9986315285466958</v>
+        <v>0.9999087364940561</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0002841228200689102</v>
+        <v>0.0001100966324200179</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2493901421667388</v>
+        <v>0.2007524016967964</v>
       </c>
       <c r="I22" t="n">
-        <v>0.001148446699257505</v>
+        <v>1.368724256749439e-05</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0006020307072949637</v>
+        <v>9.179063526686192e-05</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0008752365906446255</v>
+        <v>5.273893891717815e-05</v>
       </c>
       <c r="L22" t="n">
-        <v>0.003946879033312496</v>
+        <v>0.002101715004940108</v>
       </c>
       <c r="M22" t="n">
-        <v>0.01685594316758662</v>
+        <v>0.01049269424028061</v>
       </c>
       <c r="N22" t="n">
-        <v>1.000188305076166</v>
+        <v>1.000072967580529</v>
       </c>
       <c r="O22" t="n">
-        <v>0.01757353556484339</v>
+        <v>0.01093938995696077</v>
       </c>
       <c r="P22" t="n">
-        <v>186.3322078965155</v>
+        <v>188.2283042025219</v>
       </c>
       <c r="Q22" t="n">
-        <v>289.9366530103126</v>
+        <v>291.8327493163189</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>model_9_9_21</t>
+          <t>model_9_9_2</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9995123225518717</v>
+        <v>0.9998145407328221</v>
       </c>
       <c r="C23" t="n">
-        <v>0.5798461310269027</v>
+        <v>0.6618298626895199</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9971527409230875</v>
+        <v>0.9999485371095901</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9987554706538724</v>
+        <v>0.9998861415789512</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9986014637353372</v>
+        <v>0.9999087364940561</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0002895063997778176</v>
+        <v>0.0001100966324200179</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2494214863245302</v>
+        <v>0.2007524016967964</v>
       </c>
       <c r="I23" t="n">
-        <v>0.001177037046424638</v>
+        <v>1.368724256749439e-05</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0006118924788765066</v>
+        <v>9.179063526686192e-05</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0008944652146165319</v>
+        <v>5.273893891717815e-05</v>
       </c>
       <c r="L23" t="n">
-        <v>0.003941124086466865</v>
+        <v>0.002101715004940108</v>
       </c>
       <c r="M23" t="n">
-        <v>0.01701488759227688</v>
+        <v>0.01049269424028061</v>
       </c>
       <c r="N23" t="n">
-        <v>1.000191873094346</v>
+        <v>1.000072967580529</v>
       </c>
       <c r="O23" t="n">
-        <v>0.01773924658275302</v>
+        <v>0.01093938995696077</v>
       </c>
       <c r="P23" t="n">
-        <v>186.2946663097637</v>
+        <v>188.2283042025219</v>
       </c>
       <c r="Q23" t="n">
-        <v>289.8991114235608</v>
+        <v>291.8327493163189</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>model_9_9_22</t>
+          <t>model_9_9_1</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9995039288473578</v>
+        <v>0.9998145407328221</v>
       </c>
       <c r="C24" t="n">
-        <v>0.5797983115765717</v>
+        <v>0.6618298626895199</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9970897081153496</v>
+        <v>0.9999485371095901</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9987372106716587</v>
+        <v>0.9998861415789512</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9985740749466195</v>
+        <v>0.9999087364940561</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0002944892653664135</v>
+        <v>0.0001100966324200179</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2494498740159394</v>
+        <v>0.2007524016967964</v>
       </c>
       <c r="I24" t="n">
-        <v>0.001203094369570708</v>
+        <v>1.368724256749439e-05</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0006208702870863214</v>
+        <v>9.179063526686192e-05</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0009119823283285148</v>
+        <v>5.273893891717815e-05</v>
       </c>
       <c r="L24" t="n">
-        <v>0.00393588746759472</v>
+        <v>0.002101715004940108</v>
       </c>
       <c r="M24" t="n">
-        <v>0.01716068953644968</v>
+        <v>0.01049269424028061</v>
       </c>
       <c r="N24" t="n">
-        <v>1.000195175535466</v>
+        <v>1.000072967580529</v>
       </c>
       <c r="O24" t="n">
-        <v>0.0178912556175409</v>
+        <v>0.01093938995696077</v>
       </c>
       <c r="P24" t="n">
-        <v>186.2605360118114</v>
+        <v>188.2283042025219</v>
       </c>
       <c r="Q24" t="n">
-        <v>289.8649811256084</v>
+        <v>291.8327493163189</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>model_9_9_23</t>
+          <t>model_9_9_11</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9994961983529115</v>
+        <v>0.9998145407328221</v>
       </c>
       <c r="C25" t="n">
-        <v>0.5797549503059674</v>
+        <v>0.6618298626895199</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9970324326324681</v>
+        <v>0.9999485371095901</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9987206214936027</v>
+        <v>0.9998861415789512</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9985491870116899</v>
+        <v>0.9999087364940561</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0002990784208097083</v>
+        <v>0.0001100966324200179</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2494756151392795</v>
+        <v>0.2007524016967964</v>
       </c>
       <c r="I25" t="n">
-        <v>0.001226771654771095</v>
+        <v>1.368724256749439e-05</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0006290266180838441</v>
+        <v>9.179063526686192e-05</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0009278999649466341</v>
+        <v>5.273893891717815e-05</v>
       </c>
       <c r="L25" t="n">
-        <v>0.003931210342379961</v>
+        <v>0.002101715004940108</v>
       </c>
       <c r="M25" t="n">
-        <v>0.01729388391338708</v>
+        <v>0.01049269424028061</v>
       </c>
       <c r="N25" t="n">
-        <v>1.000198217041477</v>
+        <v>1.000072967580529</v>
       </c>
       <c r="O25" t="n">
-        <v>0.01803012035485489</v>
+        <v>0.01093938995696077</v>
       </c>
       <c r="P25" t="n">
-        <v>186.2296094840133</v>
+        <v>188.2283042025219</v>
       </c>
       <c r="Q25" t="n">
-        <v>289.8340545978103</v>
+        <v>291.8327493163189</v>
       </c>
     </row>
     <row r="26">
@@ -1837,52 +1837,52 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9994890906052737</v>
+        <v>0.9998145407328221</v>
       </c>
       <c r="C26" t="n">
-        <v>0.5797156892788542</v>
+        <v>0.6618298626895199</v>
       </c>
       <c r="D26" t="n">
-        <v>0.99698033421476</v>
+        <v>0.9999485371095901</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9987055928344877</v>
+        <v>0.9998861415789512</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9985265746052222</v>
+        <v>0.9999087364940561</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0003032978868461943</v>
+        <v>0.0001100966324200179</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2494989221809619</v>
+        <v>0.2007524016967964</v>
       </c>
       <c r="I26" t="n">
-        <v>0.001248308777332153</v>
+        <v>1.368724256749439e-05</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0006364156953351817</v>
+        <v>9.179063526686192e-05</v>
       </c>
       <c r="K26" t="n">
-        <v>0.0009423622363336675</v>
+        <v>5.273893891717815e-05</v>
       </c>
       <c r="L26" t="n">
-        <v>0.00392694901740136</v>
+        <v>0.002101715004940108</v>
       </c>
       <c r="M26" t="n">
-        <v>0.01741544965960381</v>
+        <v>0.01049269424028061</v>
       </c>
       <c r="N26" t="n">
-        <v>1.000201013532351</v>
+        <v>1.000072967580529</v>
       </c>
       <c r="O26" t="n">
-        <v>0.01815686140656385</v>
+        <v>0.01093938995696077</v>
       </c>
       <c r="P26" t="n">
-        <v>186.2015902210015</v>
+        <v>188.2283042025219</v>
       </c>
       <c r="Q26" t="n">
-        <v>289.8060353347986</v>
+        <v>291.8327493163189</v>
       </c>
     </row>
   </sheetData>
